--- a/ru/downloads/data-excel/3.5.2.1.xlsx
+++ b/ru/downloads/data-excel/3.5.2.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFF1BAC-86A3-4A07-8979-6790D3AB31B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="1470" windowWidth="17055" windowHeight="12990"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="42">
   <si>
     <t>Кыргызская Республика</t>
   </si>
   <si>
-    <t>женщины</t>
-  </si>
-  <si>
-    <t>мужчины</t>
-  </si>
-  <si>
     <t>Баткенская область</t>
   </si>
   <si>
@@ -68,12 +63,6 @@
     <t>Кыргыз Республикасы</t>
   </si>
   <si>
-    <t>аялдар</t>
-  </si>
-  <si>
-    <t>эркектер</t>
-  </si>
-  <si>
     <t>Баткен облусу</t>
   </si>
   <si>
@@ -104,12 +93,6 @@
     <t>Kyrgyz Republic</t>
   </si>
   <si>
-    <t>woman</t>
-  </si>
-  <si>
-    <t>men</t>
-  </si>
-  <si>
     <t>Batken oblast</t>
   </si>
   <si>
@@ -141,16 +124,43 @@
   </si>
   <si>
     <t>3.5.2.1 Incidence of alcohol dependence per 100,000 population by gender and territory</t>
+  </si>
+  <si>
+    <t>Көрсөткүчтөрдүн аталышы</t>
+  </si>
+  <si>
+    <t>Наименование показателей</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Аялдар</t>
+  </si>
+  <si>
+    <t>Женщины</t>
+  </si>
+  <si>
+    <t>Woman</t>
+  </si>
+  <si>
+    <t>Эркектер</t>
+  </si>
+  <si>
+    <t>Мужчины</t>
+  </si>
+  <si>
+    <t>Men</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +196,19 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -242,32 +265,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -547,23 +566,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P37"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.140625" style="3" customWidth="1"/>
     <col min="4" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
@@ -574,7 +593,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -586,14 +605,22 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-    </row>
-    <row r="3" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="16"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>35</v>
+      </c>
       <c r="D3" s="5">
         <v>2010</v>
       </c>
@@ -618,69 +645,81 @@
       <c r="K3" s="5">
         <v>2019</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="5">
         <v>2020</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="5">
         <v>2021</v>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="5">
         <v>2022</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O3" s="5">
+        <v>2023</v>
+      </c>
+      <c r="P3" s="13">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="7">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6">
         <v>53.8</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>31.2</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>27.4</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>23.5</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="6">
         <v>28.4</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="6">
         <v>23</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>18.600000000000001</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="12">
         <v>18.446483900370399</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="12">
         <v>15.121199070053857</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="12">
         <v>16.60175395812114</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="12">
         <v>11.927942610539198</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" s="12">
+        <v>12.380717630902497</v>
+      </c>
+      <c r="P4" s="15">
+        <v>9.457386925377202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2">
         <v>13.1</v>
@@ -700,31 +739,37 @@
       <c r="I5" s="2">
         <v>6.8</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="7">
         <v>4</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="7">
         <v>4.9186955004695818</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="7">
         <v>4.0418020313117182</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="7">
         <v>7.3576531459900787</v>
       </c>
-      <c r="N5" s="15">
+      <c r="N5" s="7">
         <v>3.0909744679837434</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5" s="7">
+        <v>2.5639860842442221</v>
+      </c>
+      <c r="P5" s="18">
+        <v>1.863587581490848</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D6" s="2">
         <v>95.6</v>
@@ -747,28 +792,34 @@
       <c r="J6" s="2">
         <v>33.5</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="7">
         <v>32.182343723662605</v>
       </c>
-      <c r="L6" s="15">
+      <c r="L6" s="7">
         <v>26.038712293651503</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="7">
         <v>25.982831460241147</v>
       </c>
-      <c r="N6" s="15">
+      <c r="N6" s="7">
         <v>20.963679772397647</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O6" s="7">
+        <v>22.411519350083026</v>
+      </c>
+      <c r="P6" s="18">
+        <v>17.212465071290392</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2">
         <v>27.4</v>
@@ -791,28 +842,34 @@
       <c r="J7" s="2">
         <v>6.9</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="7">
         <v>7.7177196961853767</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="7">
         <v>6.6322037707763002</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="7">
         <v>4.6978046797362003</v>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="7">
         <v>4.6002717699014832</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="7">
+        <v>5.7179491622338121</v>
+      </c>
+      <c r="P7" s="15">
+        <v>5.9419017820612288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2">
         <v>1.9</v>
@@ -835,28 +892,34 @@
       <c r="J8" s="2">
         <v>0.8</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="7">
         <v>1.9186124594693119</v>
       </c>
-      <c r="L8" s="15">
+      <c r="L8" s="7">
         <v>0.72337439688659655</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="7">
         <v>0.36820478077087354</v>
       </c>
-      <c r="N8" s="15">
+      <c r="N8" s="7">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="14">
+        <v>0.34345495073138732</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2">
         <v>52.2</v>
@@ -879,28 +942,34 @@
       <c r="J9" s="2">
         <v>12.9</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="7">
         <v>13.301803133313628</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="7">
         <v>12.766404830206815</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="7">
         <v>8.8695886639561206</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="7">
         <v>9.112830865859129</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="7">
+        <v>11.316135094078232</v>
+      </c>
+      <c r="P9" s="14">
+        <v>11.414068846977621</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D10" s="2">
         <v>17.2</v>
@@ -923,28 +992,34 @@
       <c r="J10" s="2">
         <v>6.8</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="7">
         <v>4.5654952910177142</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="7">
         <v>3.4408726052927023</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="7">
         <v>4.8763798385289059</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="7">
         <v>3.5391993253978327</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="7">
+        <v>5.0626254322122008</v>
+      </c>
+      <c r="P10" s="15">
+        <v>4.0083492430158225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2">
         <v>1.2</v>
@@ -967,28 +1042,34 @@
       <c r="J11" s="2">
         <v>1.3</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="7">
         <v>0.49230042140916069</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="7">
         <v>0.31797968427797146</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="7">
         <v>0.63362020488109327</v>
       </c>
-      <c r="N11" s="15">
+      <c r="N11" s="7">
         <v>0.30955295909412422</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="7">
+        <v>0</v>
+      </c>
+      <c r="P11" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2">
         <v>33.200000000000003</v>
@@ -1011,28 +1092,34 @@
       <c r="J12" s="2">
         <v>12.2</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="7">
         <v>8.5870565514380885</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="7">
         <v>6.6053177641160472</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="7">
         <v>9.0604897038469581</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="7">
         <v>6.73157537222552</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="7">
+        <v>10.059878800982565</v>
+      </c>
+      <c r="P12" s="14">
+        <v>7.9598117946722331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2">
         <v>19</v>
@@ -1055,28 +1142,34 @@
       <c r="J13" s="2">
         <v>3.7</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="7">
         <v>6.086340831028977</v>
       </c>
-      <c r="L13" s="15">
+      <c r="L13" s="7">
         <v>3.8076839061225556</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="7">
         <v>6.1518067459522099</v>
       </c>
-      <c r="N13" s="15">
+      <c r="N13" s="7">
         <v>3.9173330796393815</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="7">
+        <v>4.9873100666082966</v>
+      </c>
+      <c r="P13" s="15">
+        <v>0.36557524178232553</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D14" s="2">
         <v>3.1</v>
@@ -1099,28 +1192,34 @@
       <c r="J14" s="2">
         <v>1.2</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="7">
         <v>1.2124102311258036</v>
       </c>
-      <c r="L14" s="15">
+      <c r="L14" s="7">
         <v>0.40244525738386439</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="7">
         <v>2.7662407973096332</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="7">
         <v>0.7444796831494469</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="7">
+        <v>1.8457949100359559</v>
+      </c>
+      <c r="P14" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D15" s="2">
         <v>35.1</v>
@@ -1143,28 +1242,34 @@
       <c r="J15" s="2">
         <v>6.2</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="7">
         <v>10.999486690621104</v>
       </c>
-      <c r="L15" s="15">
+      <c r="L15" s="7">
         <v>7.1853419025188616</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="7">
         <v>9.5668603955896767</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="7">
         <v>7.104530072727953</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="7">
+        <v>8.1334476945372813</v>
+      </c>
+      <c r="P15" s="14">
+        <v>0.73070838524407489</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2">
         <v>31.1</v>
@@ -1187,28 +1292,34 @@
       <c r="J16" s="2">
         <v>16.100000000000001</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="7">
         <v>23.236859902543916</v>
       </c>
-      <c r="L16" s="15">
+      <c r="L16" s="7">
         <v>21.314558187024932</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="7">
         <v>19.43893106341184</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="7">
         <v>23.0957399744971</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="7">
+        <v>22.88786878481535</v>
+      </c>
+      <c r="P16" s="15">
+        <v>15.950082621427979</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2">
         <v>5.4</v>
@@ -1231,28 +1342,34 @@
       <c r="J17" s="2">
         <v>2.1</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="7">
         <v>3.5320462556777645</v>
       </c>
-      <c r="L17" s="15">
+      <c r="L17" s="7">
         <v>6.076523688314845</v>
       </c>
-      <c r="M17" s="15">
+      <c r="M17" s="7">
         <v>6.948932296552635</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="7">
         <v>2.6274648905004008</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="7">
+        <v>5.8684680690131845</v>
+      </c>
+      <c r="P17" s="14">
+        <v>4.5276965667123754</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D18" s="2">
         <v>56</v>
@@ -1275,28 +1392,34 @@
       <c r="J18" s="2">
         <v>29.6</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="7">
         <v>42.241813945249156</v>
       </c>
-      <c r="L18" s="15">
+      <c r="L18" s="7">
         <v>37.122644813336137</v>
       </c>
-      <c r="M18" s="15">
+      <c r="M18" s="7">
         <v>31.476235442241109</v>
       </c>
-      <c r="N18" s="15">
+      <c r="N18" s="7">
         <v>43.176223433734158</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="7">
+        <v>39.529219744207694</v>
+      </c>
+      <c r="P18" s="14">
+        <v>27.065473268124425</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D19" s="2">
         <v>35</v>
@@ -1319,28 +1442,34 @@
       <c r="J19" s="2">
         <v>23.2</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="7">
         <v>20.960059278590187</v>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="7">
         <v>17.175755080979702</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="7">
         <v>17.246785826277829</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N19" s="7">
         <v>7.6660105666632132</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="7">
+        <v>14.438328678723463</v>
+      </c>
+      <c r="P19" s="15">
+        <v>12.240459558090944</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D20" s="2">
         <v>2.9</v>
@@ -1363,28 +1492,34 @@
       <c r="J20" s="2">
         <v>2.1</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="7">
         <v>1.9402927155441327</v>
       </c>
-      <c r="L20" s="15">
+      <c r="L20" s="7">
         <v>1.8631795589137379</v>
       </c>
-      <c r="M20" s="15">
+      <c r="M20" s="7">
         <v>1.7299267231872171</v>
       </c>
-      <c r="N20" s="15">
+      <c r="N20" s="7">
         <v>0.83437630371297455</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="7">
+        <v>1.0926961457875199</v>
+      </c>
+      <c r="P20" s="14">
+        <v>1.0069276623167391</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2">
         <v>66.7</v>
@@ -1407,28 +1542,34 @@
       <c r="J21" s="2">
         <v>43.8</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="7">
         <v>39.564585170434306</v>
       </c>
-      <c r="L21" s="15">
+      <c r="L21" s="7">
         <v>32.838796692664047</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21" s="7">
         <v>32.417697807858893</v>
       </c>
-      <c r="N21" s="15">
+      <c r="N21" s="7">
         <v>14.406256431364477</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="7">
+        <v>27.58691223055661</v>
+      </c>
+      <c r="P21" s="14">
+        <v>23.23969847547578</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D22" s="2">
         <v>43</v>
@@ -1448,31 +1589,37 @@
       <c r="I22" s="2">
         <v>40.1</v>
       </c>
-      <c r="J22" s="9">
+      <c r="J22" s="7">
         <v>26</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="7">
         <v>27.882861836651646</v>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="7">
         <v>26.748199140342599</v>
       </c>
-      <c r="M22" s="15">
+      <c r="M22" s="7">
         <v>13.57738374823861</v>
       </c>
-      <c r="N22" s="15">
+      <c r="N22" s="7">
         <v>34.201612992199827</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="7">
+        <v>38.863020564712379</v>
+      </c>
+      <c r="P22" s="15">
+        <v>15.06434627910647</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D23" s="2">
         <v>2.6</v>
@@ -1495,28 +1642,34 @@
       <c r="J23" s="2">
         <v>3.1</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="7">
         <v>5.3348372493579141</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="7">
         <v>8.819184666377593</v>
       </c>
-      <c r="M23" s="15">
+      <c r="M23" s="7">
         <v>1.4831184047578438</v>
       </c>
-      <c r="N23" s="15">
+      <c r="N23" s="7">
         <v>4.4521615244201058</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="7">
+        <v>5.8658337182786706</v>
+      </c>
+      <c r="P23" s="14">
+        <v>2.9007998955712035</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D24" s="2">
         <v>83.1</v>
@@ -1539,28 +1692,34 @@
       <c r="J24" s="2">
         <v>48.5</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="7">
         <v>49.931809543682881</v>
       </c>
-      <c r="L24" s="15">
+      <c r="L24" s="7">
         <v>45.075501464953796</v>
       </c>
-      <c r="M24" s="15">
+      <c r="M24" s="7">
         <v>25.424775353949197</v>
       </c>
-      <c r="N24" s="15">
+      <c r="N24" s="7">
         <v>63.433733622066185</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="7">
+        <v>71.252240127246424</v>
+      </c>
+      <c r="P24" s="14">
+        <v>26.967376571027103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D25" s="2">
         <v>60.6</v>
@@ -1583,28 +1742,34 @@
       <c r="J25" s="2">
         <v>26.4</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="7">
         <v>32.298484285787929</v>
       </c>
-      <c r="L25" s="15">
+      <c r="L25" s="7">
         <v>22.63720315804489</v>
       </c>
-      <c r="M25" s="15">
+      <c r="M25" s="7">
         <v>28.259337058396849</v>
       </c>
-      <c r="N25" s="15">
+      <c r="N25" s="7">
         <v>20.535408979625672</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="7">
+        <v>15.123792416206767</v>
+      </c>
+      <c r="P25" s="15">
+        <v>15.34604289841127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D26" s="2">
         <v>20.100000000000001</v>
@@ -1627,28 +1792,34 @@
       <c r="J26" s="2">
         <v>8.1999999999999993</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="7">
         <v>13.268428603414963</v>
       </c>
-      <c r="L26" s="15">
+      <c r="L26" s="7">
         <v>6.5075739764215905</v>
       </c>
-      <c r="M26" s="15">
+      <c r="M26" s="7">
         <v>18.681751343880823</v>
       </c>
-      <c r="N26" s="15">
+      <c r="N26" s="7">
         <v>7.8632542639432348</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="7">
+        <v>5.3473569305433655</v>
+      </c>
+      <c r="P26" s="14">
+        <v>4.5589429883456845</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D27" s="2">
         <v>102.6</v>
@@ -1671,28 +1842,34 @@
       <c r="J27" s="2">
         <v>45.1</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="7">
         <v>51.905220639908066</v>
       </c>
-      <c r="L27" s="15">
+      <c r="L27" s="7">
         <v>38.284059576513137</v>
       </c>
-      <c r="M27" s="15">
+      <c r="M27" s="7">
         <v>38.14301557851968</v>
       </c>
-      <c r="N27" s="15">
+      <c r="N27" s="7">
         <v>33.368028499329796</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="7">
+        <v>25.025772810805158</v>
+      </c>
+      <c r="P27" s="14">
+        <v>26.149216561170491</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2">
         <v>164.9</v>
@@ -1715,28 +1892,34 @@
       <c r="J28" s="2">
         <v>29.7</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="7">
         <v>29.118376290145878</v>
       </c>
-      <c r="L28" s="15">
+      <c r="L28" s="7">
         <v>23.966278037020849</v>
       </c>
-      <c r="M28" s="15">
+      <c r="M28" s="7">
         <v>29.550909035673744</v>
       </c>
-      <c r="N28" s="15">
+      <c r="N28" s="7">
         <v>19.301652062045072</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="7">
+        <v>13.416777030477725</v>
+      </c>
+      <c r="P28" s="15">
+        <v>11.159255570646879</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D29" s="2">
         <v>50.1</v>
@@ -1759,28 +1942,34 @@
       <c r="J29" s="2">
         <v>9.1</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="7">
         <v>9.2276460274983858</v>
       </c>
-      <c r="L29" s="15">
+      <c r="L29" s="7">
         <v>11.409880956908683</v>
       </c>
-      <c r="M29" s="15">
+      <c r="M29" s="7">
         <v>19.441305483663228</v>
       </c>
-      <c r="N29" s="15">
+      <c r="N29" s="7">
         <v>7.1220113855063829</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="7">
+        <v>3.6371744531191936</v>
+      </c>
+      <c r="P29" s="14">
+        <v>2.8010890634278609</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D30" s="2">
         <v>297.5</v>
@@ -1800,31 +1989,37 @@
       <c r="I30" s="2">
         <v>56.3</v>
       </c>
-      <c r="J30" s="9">
+      <c r="J30" s="7">
         <v>53</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="7">
         <v>51.650669306589769</v>
       </c>
-      <c r="L30" s="15">
+      <c r="L30" s="7">
         <v>35.079762166299332</v>
       </c>
-      <c r="M30" s="15">
+      <c r="M30" s="7">
         <v>40.966897178968502</v>
       </c>
-      <c r="N30" s="15">
+      <c r="N30" s="7">
         <v>34.008685896558866</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="7">
+        <v>25.243301441354266</v>
+      </c>
+      <c r="P30" s="14">
+        <v>21.200592943567724</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D31" s="2">
         <v>29.9</v>
@@ -1847,72 +2042,84 @@
       <c r="J31" s="2">
         <v>25.2</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="7">
         <v>9.4773409849244921</v>
       </c>
-      <c r="L31" s="15">
+      <c r="L31" s="7">
         <v>16.385848928775125</v>
       </c>
-      <c r="M31" s="15">
+      <c r="M31" s="7">
         <v>17.68853538926977</v>
       </c>
-      <c r="N31" s="15">
+      <c r="N31" s="7">
         <v>7.8668258762379715</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D32" s="10">
+      <c r="O31" s="7">
+        <v>11.81299209353692</v>
+      </c>
+      <c r="P31" s="15">
+        <v>7.2594816303087626</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="2">
         <v>4.5</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="2">
         <v>2.9</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="2">
         <v>5.8</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="2">
         <v>2.8</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="2">
         <v>2.1</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="7">
         <v>2</v>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="7">
         <v>4</v>
       </c>
-      <c r="K32" s="9">
+      <c r="K32" s="7">
         <v>3.1715021502784575</v>
       </c>
-      <c r="L32" s="15">
+      <c r="L32" s="7">
         <v>3.2448358437546645</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="7">
         <v>4.1574114768313395</v>
       </c>
-      <c r="N32" s="15">
+      <c r="N32" s="7">
         <v>1.7266187050359711</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O32" s="7">
+        <v>5.6245500359971201</v>
+      </c>
+      <c r="P32" s="14">
+        <v>3.0263203403313388</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D33" s="4">
         <v>57.5</v>
@@ -1935,20 +2142,26 @@
       <c r="J33" s="4">
         <v>47.8</v>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="8">
         <v>16.179157200736149</v>
       </c>
-      <c r="L33" s="16">
+      <c r="L33" s="8">
         <v>28.789140981035917</v>
       </c>
-      <c r="M33" s="16">
+      <c r="M33" s="8">
         <v>31.970511904314137</v>
       </c>
-      <c r="N33" s="16">
+      <c r="N33" s="8">
         <v>13.723068478111704</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="8">
+        <v>17.721546178053206</v>
+      </c>
+      <c r="P33" s="17">
+        <v>11.390050158406067</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -1960,9 +2173,9 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-      <c r="N34" s="18"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N34" s="10"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1975,7 +2188,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1988,7 +2201,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
